--- a/Result/profitability/3264.xlsx
+++ b/Result/profitability/3264.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.83</v>
       </c>
       <c r="M2" t="n">
-        <v>1.36375</v>
+        <v>1.52</v>
       </c>
       <c r="N2" t="n">
-        <v>35.32625</v>
+        <v>36.66375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.6</v>
       </c>
       <c r="M3" t="n">
-        <v>1.29</v>
+        <v>1.4775</v>
       </c>
       <c r="N3" t="n">
-        <v>36.02875</v>
+        <v>37.6125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.89</v>
       </c>
       <c r="M4" t="n">
-        <v>1.28375</v>
+        <v>1.43</v>
       </c>
       <c r="N4" t="n">
-        <v>38.15</v>
+        <v>38.78125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.23</v>
       </c>
       <c r="M5" t="n">
-        <v>1.15375</v>
+        <v>1.31</v>
       </c>
       <c r="N5" t="n">
-        <v>36.28125</v>
+        <v>36.7625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.52</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.02625</v>
       </c>
       <c r="N6" t="n">
-        <v>25.22125</v>
+        <v>25.78125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.16</v>
       </c>
       <c r="M7" t="n">
-        <v>0.74125</v>
+        <v>0.8224999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>23.51625</v>
+        <v>23.80875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>0.53</v>
       </c>
       <c r="M8" t="n">
-        <v>0.58375</v>
+        <v>0.6449999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>23.0975</v>
+        <v>23.32375</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>4534</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2713</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1821</v>
+      </c>
+      <c r="F75" t="n">
+        <v>40.17</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1377</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>30.38%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>81</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1458</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1156</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.565</v>
+      </c>
+      <c r="N75" t="n">
+        <v>35.0575</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2512820512820513</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.810000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.04718456725755993</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.050420168067227</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.850000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1060022026431719</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
